--- a/artfynd/A 13636-2024 artfynd.xlsx
+++ b/artfynd/A 13636-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137445063</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137445064</v>
       </c>
       <c r="B3" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13636-2024 artfynd.xlsx
+++ b/artfynd/A 13636-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137445063</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,6 +709,9 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>St. Svaltjärnen, Vrm</t>
@@ -769,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Jens Johansen, Juno Katainen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +799,7 @@
         <v>137445064</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,6 +825,9 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>St. Svaltjärnen, Vrm</t>
@@ -881,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,7 +900,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Jens Johansen, Juno Katainen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 13636-2024 artfynd.xlsx
+++ b/artfynd/A 13636-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137445063</v>
       </c>
       <c r="B2" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137445064</v>
       </c>
       <c r="B3" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
